--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0002T0006Z000C1N36_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0002T0006Z000C1N36_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>56.93363756341489</v>
+        <v>9.251716104054919</v>
       </c>
       <c r="D2" t="n">
-        <v>56.84986488555088</v>
+        <v>9.238103043902019</v>
       </c>
       <c r="E2" t="n">
-        <v>25.00439732354754</v>
+        <v>4.063214565076475</v>
       </c>
       <c r="F2" t="n">
-        <v>24.94152600840091</v>
+        <v>4.052997976365147</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>4.640981996826086</v>
+        <v>0.754159574484239</v>
       </c>
       <c r="D3" t="n">
-        <v>4.771467961063985</v>
+        <v>0.7753635436728976</v>
       </c>
       <c r="E3" t="n">
-        <v>25.00439732354754</v>
+        <v>4.063214565076475</v>
       </c>
       <c r="F3" t="n">
-        <v>24.94152600840091</v>
+        <v>4.052997976365147</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>3.172130708497186</v>
+        <v>0.5154712401307928</v>
       </c>
       <c r="D4" t="n">
-        <v>3.147709808792769</v>
+        <v>0.5115028439288249</v>
       </c>
       <c r="E4" t="n">
-        <v>25.00439732354754</v>
+        <v>4.063214565076475</v>
       </c>
       <c r="F4" t="n">
-        <v>24.94152600840091</v>
+        <v>4.052997976365147</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
